--- a/Kwartaalrapportage/mapping.xlsx
+++ b/Kwartaalrapportage/mapping.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tgf-my.sharepoint.com/personal/tom_meijer_theglobalfund_org/Documents/Documents/Temp/Blueplates/Rapportage/Q1 2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommeijer/Git/Kwartaalrapportage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="8_{1FB977B2-70C2-624D-860F-13DEBA57CD9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6533735E-A74B-9546-9784-B1D9CD33C17D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D4D81DE-13C5-614B-B4E9-9B7BDD2174F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{5C525019-9F0A-F347-8941-DBC16E852F99}"/>
+    <workbookView xWindow="-38400" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{5C525019-9F0A-F347-8941-DBC16E852F99}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="228">
   <si>
     <t>Organisatie</t>
   </si>
@@ -720,6 +720,9 @@
   </si>
   <si>
     <t>OOY Vehicles B.V.</t>
+  </si>
+  <si>
+    <t>Inverse</t>
   </si>
 </sst>
 </file>
@@ -783,7 +786,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -803,14 +806,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B4644730-960F-1F40-9A25-5B0C1337D3E6}" name="Table1" displayName="Table1" ref="B2:F192" totalsRowShown="0">
-  <autoFilter ref="B2:F192" xr:uid="{B4644730-960F-1F40-9A25-5B0C1337D3E6}"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B4644730-960F-1F40-9A25-5B0C1337D3E6}" name="Table1" displayName="Table1" ref="B2:G192" totalsRowShown="0">
+  <autoFilter ref="B2:G192" xr:uid="{B4644730-960F-1F40-9A25-5B0C1337D3E6}"/>
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{F6CA1CCE-D776-6F48-AD4F-E85CD9F4FFE9}" name="Organisatie"/>
     <tableColumn id="2" xr3:uid="{49FDC0D0-0155-B246-A983-BC798FE84241}" name="Rekening"/>
     <tableColumn id="3" xr3:uid="{8EDA4545-FD9E-7C46-BDE1-10BC170EDC89}" name="Soort"/>
     <tableColumn id="5" xr3:uid="{37F3E3F3-C665-CB4E-BC7A-9AC0BA3AE8FF}" name="Omschrijving"/>
     <tableColumn id="4" xr3:uid="{C54F81F5-7E20-784C-B886-D34B9ED0E4B5}" name="Mapping"/>
+    <tableColumn id="6" xr3:uid="{61B739DA-4BFA-BC4F-8C81-F5EBDC5E2849}" name="Inverse"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1133,7 +1137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1093E626-7819-554A-91E3-73245727DD03}">
-  <dimension ref="B2:F192"/>
+  <dimension ref="B2:G192"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="4.42578125" customWidth="1"/>
@@ -1142,7 +1146,7 @@
     <col min="6" max="6" width="24.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6">
+    <row r="2" spans="2:7">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -1158,8 +1162,11 @@
       <c r="F2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="2:6">
+      <c r="G2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7">
       <c r="B3" t="s">
         <v>4</v>
       </c>
@@ -1175,8 +1182,11 @@
       <c r="F3" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="4" spans="2:6">
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7">
       <c r="B4" t="s">
         <v>4</v>
       </c>
@@ -1192,8 +1202,11 @@
       <c r="F4" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="5" spans="2:6">
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7">
       <c r="B5" t="s">
         <v>4</v>
       </c>
@@ -1209,8 +1222,11 @@
       <c r="F5" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="6" spans="2:6">
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7">
       <c r="B6" t="s">
         <v>4</v>
       </c>
@@ -1226,8 +1242,11 @@
       <c r="F6" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="7" spans="2:6">
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7">
       <c r="B7" t="s">
         <v>4</v>
       </c>
@@ -1243,8 +1262,11 @@
       <c r="F7" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="8" spans="2:6">
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7">
       <c r="B8" t="s">
         <v>4</v>
       </c>
@@ -1260,8 +1282,11 @@
       <c r="F8" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="9" spans="2:6">
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7">
       <c r="B9" t="s">
         <v>4</v>
       </c>
@@ -1277,8 +1302,11 @@
       <c r="F9" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="10" spans="2:6">
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7">
       <c r="B10" t="s">
         <v>4</v>
       </c>
@@ -1294,8 +1322,11 @@
       <c r="F10" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="11" spans="2:6">
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7">
       <c r="B11" t="s">
         <v>4</v>
       </c>
@@ -1311,8 +1342,11 @@
       <c r="F11" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="12" spans="2:6">
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7">
       <c r="B12" t="s">
         <v>4</v>
       </c>
@@ -1328,8 +1362,11 @@
       <c r="F12" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="13" spans="2:6">
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7">
       <c r="B13" t="s">
         <v>4</v>
       </c>
@@ -1345,8 +1382,11 @@
       <c r="F13" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="14" spans="2:6">
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7">
       <c r="B14" t="s">
         <v>4</v>
       </c>
@@ -1362,8 +1402,11 @@
       <c r="F14" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="15" spans="2:6">
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7">
       <c r="B15" t="s">
         <v>4</v>
       </c>
@@ -1379,8 +1422,11 @@
       <c r="F15" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="16" spans="2:6">
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7">
       <c r="B16" t="s">
         <v>4</v>
       </c>
@@ -1396,8 +1442,11 @@
       <c r="F16" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="17" spans="2:6">
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
       <c r="B17" t="s">
         <v>4</v>
       </c>
@@ -1413,8 +1462,11 @@
       <c r="F17" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="18" spans="2:6">
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
       <c r="B18" t="s">
         <v>4</v>
       </c>
@@ -1430,8 +1482,11 @@
       <c r="F18" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="19" spans="2:6">
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
       <c r="B19" t="s">
         <v>4</v>
       </c>
@@ -1447,8 +1502,11 @@
       <c r="F19" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="20" spans="2:6">
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7">
       <c r="B20" t="s">
         <v>4</v>
       </c>
@@ -1464,8 +1522,11 @@
       <c r="F20" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="21" spans="2:6">
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7">
       <c r="B21" t="s">
         <v>4</v>
       </c>
@@ -1481,8 +1542,11 @@
       <c r="F21" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="22" spans="2:6">
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7">
       <c r="B22" t="s">
         <v>4</v>
       </c>
@@ -1498,8 +1562,11 @@
       <c r="F22" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="23" spans="2:6">
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7">
       <c r="B23" t="s">
         <v>4</v>
       </c>
@@ -1515,8 +1582,11 @@
       <c r="F23" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="24" spans="2:6">
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7">
       <c r="B24" t="s">
         <v>4</v>
       </c>
@@ -1532,8 +1602,11 @@
       <c r="F24" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="25" spans="2:6">
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7">
       <c r="B25" t="s">
         <v>4</v>
       </c>
@@ -1549,8 +1622,11 @@
       <c r="F25" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="26" spans="2:6">
+      <c r="G25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7">
       <c r="B26" t="s">
         <v>4</v>
       </c>
@@ -1566,8 +1642,11 @@
       <c r="F26" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="27" spans="2:6">
+      <c r="G26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7">
       <c r="B27" t="s">
         <v>4</v>
       </c>
@@ -1583,8 +1662,11 @@
       <c r="F27" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="28" spans="2:6">
+      <c r="G27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7">
       <c r="B28" t="s">
         <v>4</v>
       </c>
@@ -1600,8 +1682,11 @@
       <c r="F28" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="29" spans="2:6">
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7">
       <c r="B29" t="s">
         <v>4</v>
       </c>
@@ -1617,8 +1702,11 @@
       <c r="F29" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="30" spans="2:6">
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7">
       <c r="B30" t="s">
         <v>4</v>
       </c>
@@ -1634,8 +1722,11 @@
       <c r="F30" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="31" spans="2:6">
+      <c r="G30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7">
       <c r="B31" t="s">
         <v>4</v>
       </c>
@@ -1651,8 +1742,11 @@
       <c r="F31" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="32" spans="2:6">
+      <c r="G31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7">
       <c r="B32" t="s">
         <v>4</v>
       </c>
@@ -1668,8 +1762,11 @@
       <c r="F32" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="33" spans="2:6">
+      <c r="G32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7">
       <c r="B33" t="s">
         <v>4</v>
       </c>
@@ -1685,8 +1782,11 @@
       <c r="F33" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="34" spans="2:6">
+      <c r="G33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7">
       <c r="B34" t="s">
         <v>4</v>
       </c>
@@ -1702,8 +1802,11 @@
       <c r="F34" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="35" spans="2:6">
+      <c r="G34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
       <c r="B35" t="s">
         <v>4</v>
       </c>
@@ -1719,8 +1822,11 @@
       <c r="F35" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="36" spans="2:6">
+      <c r="G35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7">
       <c r="B36" t="s">
         <v>4</v>
       </c>
@@ -1736,8 +1842,11 @@
       <c r="F36" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="37" spans="2:6">
+      <c r="G36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7">
       <c r="B37" t="s">
         <v>4</v>
       </c>
@@ -1753,8 +1862,11 @@
       <c r="F37" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="38" spans="2:6">
+      <c r="G37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7">
       <c r="B38" t="s">
         <v>4</v>
       </c>
@@ -1770,8 +1882,11 @@
       <c r="F38" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="39" spans="2:6">
+      <c r="G38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7">
       <c r="B39" t="s">
         <v>4</v>
       </c>
@@ -1787,8 +1902,11 @@
       <c r="F39" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="40" spans="2:6">
+      <c r="G39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7">
       <c r="B40" t="s">
         <v>4</v>
       </c>
@@ -1804,8 +1922,11 @@
       <c r="F40" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="41" spans="2:6">
+      <c r="G40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7">
       <c r="B41" t="s">
         <v>4</v>
       </c>
@@ -1821,8 +1942,11 @@
       <c r="F41" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="42" spans="2:6">
+      <c r="G41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7">
       <c r="B42" t="s">
         <v>4</v>
       </c>
@@ -1838,8 +1962,11 @@
       <c r="F42" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="43" spans="2:6">
+      <c r="G42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7">
       <c r="B43" t="s">
         <v>4</v>
       </c>
@@ -1855,8 +1982,11 @@
       <c r="F43" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="44" spans="2:6">
+      <c r="G43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7">
       <c r="B44" t="s">
         <v>4</v>
       </c>
@@ -1872,8 +2002,11 @@
       <c r="F44" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="45" spans="2:6">
+      <c r="G44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7">
       <c r="B45" t="s">
         <v>4</v>
       </c>
@@ -1889,8 +2022,11 @@
       <c r="F45" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="46" spans="2:6">
+      <c r="G45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7">
       <c r="B46" t="s">
         <v>4</v>
       </c>
@@ -1906,8 +2042,11 @@
       <c r="F46" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="47" spans="2:6">
+      <c r="G46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7">
       <c r="B47" t="s">
         <v>4</v>
       </c>
@@ -1923,8 +2062,11 @@
       <c r="F47" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="48" spans="2:6">
+      <c r="G47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7">
       <c r="B48" t="s">
         <v>4</v>
       </c>
@@ -1940,8 +2082,11 @@
       <c r="F48" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="49" spans="2:6">
+      <c r="G48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7">
       <c r="B49" t="s">
         <v>4</v>
       </c>
@@ -1957,8 +2102,11 @@
       <c r="F49" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="50" spans="2:6">
+      <c r="G49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7">
       <c r="B50" t="s">
         <v>4</v>
       </c>
@@ -1974,8 +2122,11 @@
       <c r="F50" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="51" spans="2:6">
+      <c r="G50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7">
       <c r="B51" t="s">
         <v>4</v>
       </c>
@@ -1991,8 +2142,11 @@
       <c r="F51" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="52" spans="2:6">
+      <c r="G51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7">
       <c r="B52" t="s">
         <v>4</v>
       </c>
@@ -2008,8 +2162,11 @@
       <c r="F52" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="53" spans="2:6">
+      <c r="G52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7">
       <c r="B53" t="s">
         <v>4</v>
       </c>
@@ -2025,8 +2182,11 @@
       <c r="F53" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="54" spans="2:6">
+      <c r="G53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7">
       <c r="B54" t="s">
         <v>4</v>
       </c>
@@ -2042,8 +2202,11 @@
       <c r="F54" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="55" spans="2:6">
+      <c r="G54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7">
       <c r="B55" t="s">
         <v>4</v>
       </c>
@@ -2059,8 +2222,11 @@
       <c r="F55" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="56" spans="2:6">
+      <c r="G55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7">
       <c r="B56" t="s">
         <v>4</v>
       </c>
@@ -2076,8 +2242,11 @@
       <c r="F56" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="57" spans="2:6">
+      <c r="G56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7">
       <c r="B57" t="s">
         <v>4</v>
       </c>
@@ -2093,8 +2262,11 @@
       <c r="F57" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="58" spans="2:6">
+      <c r="G57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7">
       <c r="B58" t="s">
         <v>4</v>
       </c>
@@ -2110,8 +2282,11 @@
       <c r="F58" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="59" spans="2:6">
+      <c r="G58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7">
       <c r="B59" t="s">
         <v>4</v>
       </c>
@@ -2127,8 +2302,11 @@
       <c r="F59" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="60" spans="2:6">
+      <c r="G59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7">
       <c r="B60" t="s">
         <v>4</v>
       </c>
@@ -2144,8 +2322,11 @@
       <c r="F60" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="61" spans="2:6">
+      <c r="G60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7">
       <c r="B61" t="s">
         <v>4</v>
       </c>
@@ -2161,8 +2342,11 @@
       <c r="F61" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="62" spans="2:6">
+      <c r="G61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7">
       <c r="B62" t="s">
         <v>4</v>
       </c>
@@ -2178,8 +2362,11 @@
       <c r="F62" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="63" spans="2:6">
+      <c r="G62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7">
       <c r="B63" t="s">
         <v>4</v>
       </c>
@@ -2195,8 +2382,11 @@
       <c r="F63" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="64" spans="2:6">
+      <c r="G63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7">
       <c r="B64" t="s">
         <v>4</v>
       </c>
@@ -2212,8 +2402,11 @@
       <c r="F64" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="65" spans="2:6">
+      <c r="G64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7">
       <c r="B65" t="s">
         <v>4</v>
       </c>
@@ -2229,8 +2422,11 @@
       <c r="F65" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="66" spans="2:6">
+      <c r="G65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:7">
       <c r="B66" t="s">
         <v>4</v>
       </c>
@@ -2246,8 +2442,11 @@
       <c r="F66" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="67" spans="2:6">
+      <c r="G66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7">
       <c r="B67" t="s">
         <v>4</v>
       </c>
@@ -2263,8 +2462,11 @@
       <c r="F67" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="68" spans="2:6">
+      <c r="G67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7">
       <c r="B68" t="s">
         <v>4</v>
       </c>
@@ -2280,8 +2482,11 @@
       <c r="F68" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="69" spans="2:6">
+      <c r="G68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7">
       <c r="B69" t="s">
         <v>4</v>
       </c>
@@ -2297,8 +2502,11 @@
       <c r="F69" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="70" spans="2:6">
+      <c r="G69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7">
       <c r="B70" t="s">
         <v>4</v>
       </c>
@@ -2314,8 +2522,11 @@
       <c r="F70" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="71" spans="2:6">
+      <c r="G70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:7">
       <c r="B71" t="s">
         <v>180</v>
       </c>
@@ -2331,8 +2542,11 @@
       <c r="F71" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="72" spans="2:6">
+      <c r="G71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:7">
       <c r="B72" t="s">
         <v>180</v>
       </c>
@@ -2348,8 +2562,11 @@
       <c r="F72" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="73" spans="2:6">
+      <c r="G72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:7">
       <c r="B73" t="s">
         <v>180</v>
       </c>
@@ -2365,8 +2582,11 @@
       <c r="F73" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="74" spans="2:6">
+      <c r="G73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:7">
       <c r="B74" t="s">
         <v>180</v>
       </c>
@@ -2382,8 +2602,11 @@
       <c r="F74" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="75" spans="2:6">
+      <c r="G74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:7">
       <c r="B75" t="s">
         <v>180</v>
       </c>
@@ -2399,8 +2622,11 @@
       <c r="F75" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="76" spans="2:6">
+      <c r="G75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:7">
       <c r="B76" t="s">
         <v>180</v>
       </c>
@@ -2416,8 +2642,11 @@
       <c r="F76" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="77" spans="2:6">
+      <c r="G76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:7">
       <c r="B77" t="s">
         <v>180</v>
       </c>
@@ -2433,8 +2662,11 @@
       <c r="F77" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="78" spans="2:6">
+      <c r="G77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7">
       <c r="B78" t="s">
         <v>180</v>
       </c>
@@ -2450,8 +2682,11 @@
       <c r="F78" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="79" spans="2:6">
+      <c r="G78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:7">
       <c r="B79" t="s">
         <v>180</v>
       </c>
@@ -2467,8 +2702,11 @@
       <c r="F79" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="80" spans="2:6">
+      <c r="G79" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7">
       <c r="B80" t="s">
         <v>180</v>
       </c>
@@ -2484,8 +2722,11 @@
       <c r="F80" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="81" spans="2:6">
+      <c r="G80" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="2:7">
       <c r="B81" t="s">
         <v>180</v>
       </c>
@@ -2501,8 +2742,11 @@
       <c r="F81" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="82" spans="2:6">
+      <c r="G81" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7">
       <c r="B82" t="s">
         <v>180</v>
       </c>
@@ -2518,8 +2762,11 @@
       <c r="F82" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="83" spans="2:6">
+      <c r="G82" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="2:7">
       <c r="B83" t="s">
         <v>180</v>
       </c>
@@ -2535,8 +2782,11 @@
       <c r="F83" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="84" spans="2:6">
+      <c r="G83" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="2:7">
       <c r="B84" t="s">
         <v>180</v>
       </c>
@@ -2552,8 +2802,11 @@
       <c r="F84" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="85" spans="2:6">
+      <c r="G84" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7">
       <c r="B85" t="s">
         <v>180</v>
       </c>
@@ -2569,8 +2822,11 @@
       <c r="F85" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="86" spans="2:6">
+      <c r="G85" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="2:7">
       <c r="B86" t="s">
         <v>180</v>
       </c>
@@ -2586,8 +2842,11 @@
       <c r="F86" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="87" spans="2:6">
+      <c r="G86" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7">
       <c r="B87" t="s">
         <v>180</v>
       </c>
@@ -2603,8 +2862,11 @@
       <c r="F87" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="88" spans="2:6">
+      <c r="G87" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7">
       <c r="B88" t="s">
         <v>180</v>
       </c>
@@ -2620,8 +2882,11 @@
       <c r="F88" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="89" spans="2:6">
+      <c r="G88" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="2:7">
       <c r="B89" t="s">
         <v>180</v>
       </c>
@@ -2637,8 +2902,11 @@
       <c r="F89" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="90" spans="2:6">
+      <c r="G89" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="2:7">
       <c r="B90" t="s">
         <v>180</v>
       </c>
@@ -2654,8 +2922,11 @@
       <c r="F90" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="91" spans="2:6">
+      <c r="G90" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="2:7">
       <c r="B91" t="s">
         <v>180</v>
       </c>
@@ -2671,8 +2942,11 @@
       <c r="F91" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="92" spans="2:6">
+      <c r="G91" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="2:7">
       <c r="B92" t="s">
         <v>180</v>
       </c>
@@ -2688,8 +2962,11 @@
       <c r="F92" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="93" spans="2:6">
+      <c r="G92" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="2:7">
       <c r="B93" t="s">
         <v>180</v>
       </c>
@@ -2705,8 +2982,11 @@
       <c r="F93" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="94" spans="2:6">
+      <c r="G93" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="2:7">
       <c r="B94" t="s">
         <v>180</v>
       </c>
@@ -2722,8 +3002,11 @@
       <c r="F94" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="95" spans="2:6">
+      <c r="G94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="2:7">
       <c r="B95" t="s">
         <v>180</v>
       </c>
@@ -2739,8 +3022,11 @@
       <c r="F95" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="96" spans="2:6">
+      <c r="G95" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="2:7">
       <c r="B96" t="s">
         <v>180</v>
       </c>
@@ -2756,8 +3042,11 @@
       <c r="F96" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="97" spans="2:6">
+      <c r="G96" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7">
       <c r="B97" t="s">
         <v>180</v>
       </c>
@@ -2773,8 +3062,11 @@
       <c r="F97" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="98" spans="2:6">
+      <c r="G97" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7">
       <c r="B98" t="s">
         <v>180</v>
       </c>
@@ -2790,8 +3082,11 @@
       <c r="F98" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="99" spans="2:6">
+      <c r="G98" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7">
       <c r="B99" t="s">
         <v>180</v>
       </c>
@@ -2807,8 +3102,11 @@
       <c r="F99" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="100" spans="2:6">
+      <c r="G99" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="2:7">
       <c r="B100" t="s">
         <v>180</v>
       </c>
@@ -2824,8 +3122,11 @@
       <c r="F100" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="101" spans="2:6">
+      <c r="G100" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="2:7">
       <c r="B101" t="s">
         <v>180</v>
       </c>
@@ -2841,8 +3142,11 @@
       <c r="F101" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="102" spans="2:6">
+      <c r="G101" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="2:7">
       <c r="B102" t="s">
         <v>180</v>
       </c>
@@ -2858,8 +3162,11 @@
       <c r="F102" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="103" spans="2:6">
+      <c r="G102" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7">
       <c r="B103" t="s">
         <v>180</v>
       </c>
@@ -2875,8 +3182,11 @@
       <c r="F103" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="104" spans="2:6">
+      <c r="G103" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7">
       <c r="B104" t="s">
         <v>180</v>
       </c>
@@ -2892,8 +3202,11 @@
       <c r="F104" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="105" spans="2:6">
+      <c r="G104" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7">
       <c r="B105" t="s">
         <v>180</v>
       </c>
@@ -2909,8 +3222,11 @@
       <c r="F105" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="106" spans="2:6">
+      <c r="G105" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7">
       <c r="B106" t="s">
         <v>180</v>
       </c>
@@ -2926,8 +3242,11 @@
       <c r="F106" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="107" spans="2:6">
+      <c r="G106" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7">
       <c r="B107" t="s">
         <v>180</v>
       </c>
@@ -2943,8 +3262,11 @@
       <c r="F107" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="108" spans="2:6">
+      <c r="G107" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7">
       <c r="B108" t="s">
         <v>180</v>
       </c>
@@ -2960,8 +3282,11 @@
       <c r="F108" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="109" spans="2:6">
+      <c r="G108" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="2:7">
       <c r="B109" t="s">
         <v>209</v>
       </c>
@@ -2977,8 +3302,11 @@
       <c r="F109" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="110" spans="2:6">
+      <c r="G109" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="2:7">
       <c r="B110" t="s">
         <v>209</v>
       </c>
@@ -2994,8 +3322,11 @@
       <c r="F110" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="111" spans="2:6">
+      <c r="G110" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="2:7">
       <c r="B111" t="s">
         <v>209</v>
       </c>
@@ -3011,8 +3342,11 @@
       <c r="F111" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="112" spans="2:6">
+      <c r="G111" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="2:7">
       <c r="B112" t="s">
         <v>209</v>
       </c>
@@ -3028,8 +3362,11 @@
       <c r="F112" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="113" spans="2:6">
+      <c r="G112" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="2:7">
       <c r="B113" t="s">
         <v>209</v>
       </c>
@@ -3045,8 +3382,11 @@
       <c r="F113" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="114" spans="2:6">
+      <c r="G113" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="2:7">
       <c r="B114" t="s">
         <v>209</v>
       </c>
@@ -3062,8 +3402,11 @@
       <c r="F114" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="115" spans="2:6">
+      <c r="G114" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="2:7">
       <c r="B115" t="s">
         <v>209</v>
       </c>
@@ -3079,8 +3422,11 @@
       <c r="F115" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="116" spans="2:6">
+      <c r="G115" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="2:7">
       <c r="B116" t="s">
         <v>209</v>
       </c>
@@ -3096,8 +3442,11 @@
       <c r="F116" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="117" spans="2:6">
+      <c r="G116" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="2:7">
       <c r="B117" t="s">
         <v>209</v>
       </c>
@@ -3113,8 +3462,11 @@
       <c r="F117" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="118" spans="2:6">
+      <c r="G117" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="2:7">
       <c r="B118" t="s">
         <v>209</v>
       </c>
@@ -3130,8 +3482,11 @@
       <c r="F118" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="119" spans="2:6">
+      <c r="G118" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="2:7">
       <c r="B119" t="s">
         <v>209</v>
       </c>
@@ -3147,8 +3502,11 @@
       <c r="F119" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="120" spans="2:6">
+      <c r="G119" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="2:7">
       <c r="B120" t="s">
         <v>209</v>
       </c>
@@ -3164,8 +3522,11 @@
       <c r="F120" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="121" spans="2:6">
+      <c r="G120" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="2:7">
       <c r="B121" t="s">
         <v>209</v>
       </c>
@@ -3181,8 +3542,11 @@
       <c r="F121" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="122" spans="2:6">
+      <c r="G121" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="2:7">
       <c r="B122" t="s">
         <v>209</v>
       </c>
@@ -3198,8 +3562,11 @@
       <c r="F122" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="123" spans="2:6">
+      <c r="G122" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="2:7">
       <c r="B123" t="s">
         <v>209</v>
       </c>
@@ -3215,8 +3582,11 @@
       <c r="F123" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="124" spans="2:6">
+      <c r="G123" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="2:7">
       <c r="B124" t="s">
         <v>209</v>
       </c>
@@ -3232,8 +3602,11 @@
       <c r="F124" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="125" spans="2:6">
+      <c r="G124" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="2:7">
       <c r="B125" t="s">
         <v>209</v>
       </c>
@@ -3249,8 +3622,11 @@
       <c r="F125" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="126" spans="2:6">
+      <c r="G125" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="2:7">
       <c r="B126" t="s">
         <v>209</v>
       </c>
@@ -3266,8 +3642,11 @@
       <c r="F126" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="127" spans="2:6">
+      <c r="G126" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="2:7">
       <c r="B127" t="s">
         <v>209</v>
       </c>
@@ -3283,8 +3662,11 @@
       <c r="F127" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="128" spans="2:6">
+      <c r="G127" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="2:7">
       <c r="B128" t="s">
         <v>209</v>
       </c>
@@ -3300,8 +3682,11 @@
       <c r="F128" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="129" spans="2:6">
+      <c r="G128" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="2:7">
       <c r="B129" t="s">
         <v>209</v>
       </c>
@@ -3317,8 +3702,11 @@
       <c r="F129" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="130" spans="2:6">
+      <c r="G129" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="2:7">
       <c r="B130" t="s">
         <v>209</v>
       </c>
@@ -3334,8 +3722,11 @@
       <c r="F130" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="131" spans="2:6">
+      <c r="G130" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="2:7">
       <c r="B131" t="s">
         <v>209</v>
       </c>
@@ -3351,8 +3742,11 @@
       <c r="F131" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="132" spans="2:6">
+      <c r="G131" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="2:7">
       <c r="B132" t="s">
         <v>209</v>
       </c>
@@ -3368,8 +3762,11 @@
       <c r="F132" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="133" spans="2:6">
+      <c r="G132" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="2:7">
       <c r="B133" t="s">
         <v>209</v>
       </c>
@@ -3385,8 +3782,11 @@
       <c r="F133" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="134" spans="2:6">
+      <c r="G133" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="2:7">
       <c r="B134" t="s">
         <v>209</v>
       </c>
@@ -3402,8 +3802,11 @@
       <c r="F134" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="135" spans="2:6">
+      <c r="G134" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="2:7">
       <c r="B135" t="s">
         <v>209</v>
       </c>
@@ -3419,8 +3822,11 @@
       <c r="F135" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="136" spans="2:6">
+      <c r="G135" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="2:7">
       <c r="B136" t="s">
         <v>209</v>
       </c>
@@ -3436,8 +3842,11 @@
       <c r="F136" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="137" spans="2:6">
+      <c r="G136" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="2:7">
       <c r="B137" t="s">
         <v>209</v>
       </c>
@@ -3453,8 +3862,11 @@
       <c r="F137" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="138" spans="2:6">
+      <c r="G137" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="2:7">
       <c r="B138" t="s">
         <v>209</v>
       </c>
@@ -3470,8 +3882,11 @@
       <c r="F138" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="139" spans="2:6">
+      <c r="G138" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="2:7">
       <c r="B139" t="s">
         <v>209</v>
       </c>
@@ -3487,8 +3902,11 @@
       <c r="F139" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="140" spans="2:6">
+      <c r="G139" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="2:7">
       <c r="B140" t="s">
         <v>209</v>
       </c>
@@ -3504,8 +3922,11 @@
       <c r="F140" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="141" spans="2:6">
+      <c r="G140" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="2:7">
       <c r="B141" t="s">
         <v>209</v>
       </c>
@@ -3521,8 +3942,11 @@
       <c r="F141" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="142" spans="2:6">
+      <c r="G141" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="2:7">
       <c r="B142" t="s">
         <v>209</v>
       </c>
@@ -3538,8 +3962,11 @@
       <c r="F142" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="143" spans="2:6">
+      <c r="G142" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="2:7">
       <c r="B143" t="s">
         <v>209</v>
       </c>
@@ -3555,8 +3982,11 @@
       <c r="F143" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="144" spans="2:6">
+      <c r="G143" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="2:7">
       <c r="B144" t="s">
         <v>209</v>
       </c>
@@ -3572,8 +4002,11 @@
       <c r="F144" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="145" spans="2:6">
+      <c r="G144" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="2:7">
       <c r="B145" t="s">
         <v>209</v>
       </c>
@@ -3589,8 +4022,11 @@
       <c r="F145" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="146" spans="2:6">
+      <c r="G145" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="2:7">
       <c r="B146" t="s">
         <v>209</v>
       </c>
@@ -3606,8 +4042,11 @@
       <c r="F146" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="147" spans="2:6">
+      <c r="G146" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="2:7">
       <c r="B147" t="s">
         <v>209</v>
       </c>
@@ -3623,8 +4062,11 @@
       <c r="F147" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="148" spans="2:6">
+      <c r="G147" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="2:7">
       <c r="B148" t="s">
         <v>209</v>
       </c>
@@ -3640,8 +4082,11 @@
       <c r="F148" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="149" spans="2:6">
+      <c r="G148" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="2:7">
       <c r="B149" t="s">
         <v>209</v>
       </c>
@@ -3657,8 +4102,11 @@
       <c r="F149" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="150" spans="2:6">
+      <c r="G149" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="2:7">
       <c r="B150" t="s">
         <v>209</v>
       </c>
@@ -3674,8 +4122,11 @@
       <c r="F150" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="151" spans="2:6">
+      <c r="G150" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="2:7">
       <c r="B151" t="s">
         <v>209</v>
       </c>
@@ -3691,8 +4142,11 @@
       <c r="F151" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="152" spans="2:6">
+      <c r="G151" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="2:7">
       <c r="B152" t="s">
         <v>209</v>
       </c>
@@ -3708,8 +4162,11 @@
       <c r="F152" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="153" spans="2:6">
+      <c r="G152" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="2:7">
       <c r="B153" t="s">
         <v>226</v>
       </c>
@@ -3725,8 +4182,11 @@
       <c r="F153" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="154" spans="2:6">
+      <c r="G153" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="2:7">
       <c r="B154" t="s">
         <v>226</v>
       </c>
@@ -3742,8 +4202,11 @@
       <c r="F154" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="155" spans="2:6">
+      <c r="G154" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="2:7">
       <c r="B155" t="s">
         <v>226</v>
       </c>
@@ -3759,8 +4222,11 @@
       <c r="F155" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="156" spans="2:6">
+      <c r="G155" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="2:7">
       <c r="B156" t="s">
         <v>226</v>
       </c>
@@ -3776,8 +4242,11 @@
       <c r="F156" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="157" spans="2:6">
+      <c r="G156" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="2:7">
       <c r="B157" t="s">
         <v>226</v>
       </c>
@@ -3793,8 +4262,11 @@
       <c r="F157" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="158" spans="2:6">
+      <c r="G157" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="2:7">
       <c r="B158" t="s">
         <v>226</v>
       </c>
@@ -3810,8 +4282,11 @@
       <c r="F158" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="159" spans="2:6">
+      <c r="G158" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="2:7">
       <c r="B159" t="s">
         <v>226</v>
       </c>
@@ -3827,8 +4302,11 @@
       <c r="F159" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="160" spans="2:6">
+      <c r="G159" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="2:7">
       <c r="B160" t="s">
         <v>226</v>
       </c>
@@ -3844,8 +4322,11 @@
       <c r="F160" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="161" spans="2:6">
+      <c r="G160" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="2:7">
       <c r="B161" t="s">
         <v>226</v>
       </c>
@@ -3861,8 +4342,11 @@
       <c r="F161" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="162" spans="2:6">
+      <c r="G161" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="2:7">
       <c r="B162" t="s">
         <v>226</v>
       </c>
@@ -3878,8 +4362,11 @@
       <c r="F162" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="163" spans="2:6">
+      <c r="G162" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="2:7">
       <c r="B163" t="s">
         <v>226</v>
       </c>
@@ -3895,8 +4382,11 @@
       <c r="F163" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="164" spans="2:6">
+      <c r="G163" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="2:7">
       <c r="B164" t="s">
         <v>226</v>
       </c>
@@ -3912,8 +4402,11 @@
       <c r="F164" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="165" spans="2:6">
+      <c r="G164" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="2:7">
       <c r="B165" t="s">
         <v>226</v>
       </c>
@@ -3929,8 +4422,11 @@
       <c r="F165" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="166" spans="2:6">
+      <c r="G165" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="2:7">
       <c r="B166" t="s">
         <v>226</v>
       </c>
@@ -3946,8 +4442,11 @@
       <c r="F166" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="167" spans="2:6">
+      <c r="G166" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="2:7">
       <c r="B167" t="s">
         <v>226</v>
       </c>
@@ -3963,8 +4462,11 @@
       <c r="F167" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="168" spans="2:6">
+      <c r="G167" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="2:7">
       <c r="B168" t="s">
         <v>226</v>
       </c>
@@ -3980,8 +4482,11 @@
       <c r="F168" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="169" spans="2:6">
+      <c r="G168" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="2:7">
       <c r="B169" t="s">
         <v>226</v>
       </c>
@@ -3997,8 +4502,11 @@
       <c r="F169" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="170" spans="2:6">
+      <c r="G169" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="2:7">
       <c r="B170" t="s">
         <v>226</v>
       </c>
@@ -4014,8 +4522,11 @@
       <c r="F170" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="171" spans="2:6">
+      <c r="G170" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="2:7">
       <c r="B171" t="s">
         <v>226</v>
       </c>
@@ -4031,8 +4542,11 @@
       <c r="F171" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="172" spans="2:6">
+      <c r="G171" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="2:7">
       <c r="B172" t="s">
         <v>226</v>
       </c>
@@ -4048,8 +4562,11 @@
       <c r="F172" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="173" spans="2:6">
+      <c r="G172" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="2:7">
       <c r="B173" t="s">
         <v>226</v>
       </c>
@@ -4065,8 +4582,11 @@
       <c r="F173" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="174" spans="2:6">
+      <c r="G173" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="2:7">
       <c r="B174" t="s">
         <v>226</v>
       </c>
@@ -4082,8 +4602,11 @@
       <c r="F174" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="175" spans="2:6">
+      <c r="G174" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="2:7">
       <c r="B175" t="s">
         <v>226</v>
       </c>
@@ -4099,8 +4622,11 @@
       <c r="F175" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="176" spans="2:6">
+      <c r="G175" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="2:7">
       <c r="B176" t="s">
         <v>226</v>
       </c>
@@ -4116,8 +4642,11 @@
       <c r="F176" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="177" spans="2:6">
+      <c r="G176" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="2:7">
       <c r="B177" t="s">
         <v>226</v>
       </c>
@@ -4133,8 +4662,11 @@
       <c r="F177" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="178" spans="2:6">
+      <c r="G177" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="2:7">
       <c r="B178" t="s">
         <v>226</v>
       </c>
@@ -4150,8 +4682,11 @@
       <c r="F178" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="179" spans="2:6">
+      <c r="G178" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="2:7">
       <c r="B179" t="s">
         <v>226</v>
       </c>
@@ -4167,8 +4702,11 @@
       <c r="F179" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="180" spans="2:6">
+      <c r="G179" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="2:7">
       <c r="B180" t="s">
         <v>226</v>
       </c>
@@ -4184,8 +4722,11 @@
       <c r="F180" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="181" spans="2:6">
+      <c r="G180" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="2:7">
       <c r="B181" t="s">
         <v>226</v>
       </c>
@@ -4201,8 +4742,11 @@
       <c r="F181" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="182" spans="2:6">
+      <c r="G181" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="2:7">
       <c r="B182" t="s">
         <v>226</v>
       </c>
@@ -4218,8 +4762,11 @@
       <c r="F182" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="183" spans="2:6">
+      <c r="G182" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="2:7">
       <c r="B183" t="s">
         <v>226</v>
       </c>
@@ -4235,8 +4782,11 @@
       <c r="F183" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="184" spans="2:6">
+      <c r="G183" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="2:7">
       <c r="B184" t="s">
         <v>226</v>
       </c>
@@ -4252,8 +4802,11 @@
       <c r="F184" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="185" spans="2:6">
+      <c r="G184" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="2:7">
       <c r="B185" t="s">
         <v>226</v>
       </c>
@@ -4269,8 +4822,11 @@
       <c r="F185" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="186" spans="2:6">
+      <c r="G185" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="2:7">
       <c r="B186" t="s">
         <v>226</v>
       </c>
@@ -4286,8 +4842,11 @@
       <c r="F186" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="187" spans="2:6">
+      <c r="G186" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="2:7">
       <c r="B187" t="s">
         <v>226</v>
       </c>
@@ -4303,8 +4862,11 @@
       <c r="F187" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="188" spans="2:6">
+      <c r="G187" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="2:7">
       <c r="B188" t="s">
         <v>226</v>
       </c>
@@ -4320,8 +4882,11 @@
       <c r="F188" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="189" spans="2:6">
+      <c r="G188" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="2:7">
       <c r="B189" t="s">
         <v>226</v>
       </c>
@@ -4337,8 +4902,11 @@
       <c r="F189" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="190" spans="2:6">
+      <c r="G189" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="2:7">
       <c r="B190" t="s">
         <v>226</v>
       </c>
@@ -4354,8 +4922,11 @@
       <c r="F190" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="191" spans="2:6">
+      <c r="G190" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="2:7">
       <c r="B191" t="s">
         <v>226</v>
       </c>
@@ -4371,8 +4942,11 @@
       <c r="F191" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="192" spans="2:6">
+      <c r="G191" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="2:7">
       <c r="B192" t="s">
         <v>226</v>
       </c>
@@ -4387,6 +4961,9 @@
       </c>
       <c r="F192" t="s">
         <v>84</v>
+      </c>
+      <c r="G192" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
